--- a/task/MXSC/Resources/Pigeon_fixed_InstructionsConditions.xlsx
+++ b/task/MXSC/Resources/Pigeon_fixed_InstructionsConditions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10703"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ishankalburge/Documents/penn/pigeons-lohi-snr-v1/Resources/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jigold/Library/CloudStorage/Box-Box/GoldLab/Projects/2025_Pigeon/Code/task/MXSC/Resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAB5DB62-34E6-C84D-89FF-3D0E8B8AFBC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B134FA8D-5B00-4346-A710-756F6B9115E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="760" windowWidth="24600" windowHeight="12840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28760" yWindow="-2580" windowWidth="27240" windowHeight="19480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,56 +38,44 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
-    <t xml:space="preserve">ic_message_string</t>
-  </si>
-  <si>
-    <t xml:space="preserve">This is the fixed block. In each trial, Petey will either be foraging during the day or at night.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The time of day will be indicated by the icon in the top right of your screen.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A sun icon indicates daytime and a moon icon indicates nighttime.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Here are a few reminders:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">In the daytime, Petey is much better at foraging, so he will reach the correct pile of seeds more quickly.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">At night, Petey cannot forage as well, so he will meander more before reaching one of the piles.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">You will receive a cash bonus based on how quickly you reach the target score.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Please respond at a natural, careful pace: if your responses are consistently much faster or much slower than expected for this task, your session may end early.</t>
+    <t>ic_message_string</t>
+  </si>
+  <si>
+    <t>This is the fixed block. In each trial, Petey will either be foraging during the day or at night.</t>
+  </si>
+  <si>
+    <t>The time of day will be indicated by the icon in the top right of your screen.</t>
+  </si>
+  <si>
+    <t>A sun icon indicates daytime and a moon icon indicates nighttime.</t>
+  </si>
+  <si>
+    <t>Here are a few reminders:</t>
+  </si>
+  <si>
+    <t>In the daytime, Petey is much better at foraging, so he will reach the correct pile of seeds more quickly.</t>
+  </si>
+  <si>
+    <t>At night, Petey cannot forage as well, so he will meander more before reaching one of the piles.</t>
+  </si>
+  <si>
+    <t>Please respond at a natural, careful pace: if your responses are consistently much faster or much slower than expected for this task, your session may end early.</t>
+  </si>
+  <si>
+    <t>You may receive a bonus payment based on your final score for the block.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -98,7 +86,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -106,34 +94,15 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFCCCCCC"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -447,60 +416,60 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="30.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:1" ht="48" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:1" ht="48" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:1" ht="32" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1">
-      <c r="A5" s="2" t="s">
+    <row r="5" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
-      <c r="A6" s="2" t="s">
+    <row r="6" spans="1:1" ht="48" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:1">
-      <c r="A7" s="2" t="s">
+    <row r="7" spans="1:1" ht="48" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:1">
-      <c r="A8" s="2" t="s">
+    <row r="8" spans="1:1" ht="32" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" ht="80" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" s="2"/>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A10" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
